--- a/Result/profitability/6414.xlsx
+++ b/Result/profitability/6414.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM60"/>
+  <dimension ref="A1:AM61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7566,15 +7566,15 @@
         <v>18.22</v>
       </c>
       <c r="G57" t="n">
-        <v>-700</v>
+        <v>119</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-2.02%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3426</v>
+        <v>2608</v>
       </c>
       <c r="J57" t="n">
         <v>2726</v>
@@ -7693,15 +7693,15 @@
         <v>21.69</v>
       </c>
       <c r="G58" t="n">
-        <v>1286</v>
+        <v>468</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1369</v>
+        <v>2187</v>
       </c>
       <c r="J58" t="n">
         <v>2655</v>
@@ -8048,6 +8048,133 @@
       </c>
       <c r="AM60" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6414</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>48379</v>
+      </c>
+      <c r="D61" t="n">
+        <v>39031</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9348</v>
+      </c>
+      <c r="F61" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2685</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>5.55%</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>774</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3460</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1051</v>
+      </c>
+      <c r="L61" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="M61" t="n">
+        <v>5.91625</v>
+      </c>
+      <c r="N61" t="n">
+        <v>20.17875</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W61" t="n">
+        <v>2</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0.3883495145631068</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>-0.7899999999999991</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-0.03928393833913468</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0.7396593673965937</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.100000000000001</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.06037321624588365</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK61" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
